--- a/data/trans_orig/IP09B02-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP09B02-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si dicha enfermedad o dolencia continuada le ha afectado para realizar actividades de ocio en 2007 (tasa de respuesta: 98,55%)</t>
+          <t>Menores según si dicha enfermedad o dolencia continuada le ha afectado para realizar actividades de ocio como pasear, ir al cine, hacer deporte, etc en 2007 (tasa de respuesta: 98,55%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4144</t>
+          <t>4281</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9105</t>
+          <t>9120</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>42,44%</t>
+          <t>43,84%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11216</t>
+          <t>11808</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16269</t>
+          <t>16266</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>66,51%</t>
+          <t>70,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18097</t>
+          <t>17402</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24670</t>
+          <t>24260</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>67,96%</t>
+          <t>65,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>91,1%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>645</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5621</t>
+          <t>5484</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>57,56%</t>
+          <t>56,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>598</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5648</t>
+          <t>5056</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1960</t>
+          <t>2370</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8533</t>
+          <t>9228</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>34,65%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8701</t>
+          <t>8724</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13742</t>
+          <t>13759</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>57,91%</t>
+          <t>58,06%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16862</t>
+          <t>16589</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24343</t>
+          <t>24208</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>60,9%</t>
+          <t>59,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>87,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>27861</t>
+          <t>27523</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>36766</t>
+          <t>36194</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>65,23%</t>
+          <t>64,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>86,08%</t>
+          <t>84,74%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1284</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6325</t>
+          <t>6302</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>42,09%</t>
+          <t>41,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3343</t>
+          <t>3478</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10824</t>
+          <t>11097</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>40,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5946</t>
+          <t>6518</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>14851</t>
+          <t>15189</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>34,77%</t>
+          <t>35,56%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2556</t>
+          <t>2533</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6815</t>
+          <t>6729</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>32,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>86,6%</t>
+          <t>85,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9239</t>
+          <t>9831</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14646</t>
+          <t>14640</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>60,13%</t>
+          <t>63,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13988</t>
+          <t>13839</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20519</t>
+          <t>20305</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>60,2%</t>
+          <t>59,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>87,38%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1054</t>
+          <t>1140</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5313</t>
+          <t>5336</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>67,51%</t>
+          <t>67,81%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>726</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6127</t>
+          <t>5535</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>39,87%</t>
+          <t>36,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2717</t>
+          <t>2931</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>9248</t>
+          <t>9397</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>39,8%</t>
+          <t>40,44%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11121</t>
+          <t>11118</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19011</t>
+          <t>19111</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>48,54%</t>
+          <t>48,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>82,97%</t>
+          <t>83,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15539</t>
+          <t>15656</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20997</t>
+          <t>20968</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>69,95%</t>
+          <t>70,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>29377</t>
+          <t>29107</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>39159</t>
+          <t>38986</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>65,1%</t>
+          <t>64,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>86,78%</t>
+          <t>86,39%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3902</t>
+          <t>3802</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11792</t>
+          <t>11795</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>51,46%</t>
+          <t>51,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1218</t>
+          <t>1247</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6676</t>
+          <t>6559</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>29,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5968</t>
+          <t>6141</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>15750</t>
+          <t>16020</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>35,5%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>33568</t>
+          <t>33479</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>44653</t>
+          <t>44264</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>60,4%</t>
+          <t>60,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>80,35%</t>
+          <t>79,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>61625</t>
+          <t>61042</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>72284</t>
+          <t>72400</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>75,03%</t>
+          <t>74,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>98650</t>
+          <t>98413</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>114986</t>
+          <t>114016</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>71,64%</t>
+          <t>71,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>83,5%</t>
+          <t>82,8%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10921</t>
+          <t>11310</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>22006</t>
+          <t>22095</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>39,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9847</t>
+          <t>9731</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>20506</t>
+          <t>21089</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>22719</t>
+          <t>23689</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>39055</t>
+          <t>39292</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>28,53%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si dicha enfermedad o dolencia continuada le ha afectado para realizar actividades de ocio en 2012 (tasa de respuesta: 97,74%)</t>
+          <t>Menores según si dicha enfermedad o dolencia continuada le ha afectado para realizar actividades de ocio como pasear, ir al cine, hacer deporte, etc en 2012 (tasa de respuesta: 97,74%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7746</t>
+          <t>7715</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13361</t>
+          <t>12774</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>55,07%</t>
+          <t>54,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6831</t>
+          <t>7486</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13636</t>
+          <t>13896</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>42,3%</t>
+          <t>46,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>86,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17584</t>
+          <t>17352</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25951</t>
+          <t>25926</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>58,2%</t>
+          <t>57,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>85,89%</t>
+          <t>85,81%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>704</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6319</t>
+          <t>6350</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>44,93%</t>
+          <t>45,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2513</t>
+          <t>2253</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9318</t>
+          <t>8663</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>57,7%</t>
+          <t>53,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4263</t>
+          <t>4288</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12630</t>
+          <t>12862</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>41,8%</t>
+          <t>42,57%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12375</t>
+          <t>11829</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19760</t>
+          <t>20055</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>44,51%</t>
+          <t>42,54%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>71,06%</t>
+          <t>72,12%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11426</t>
+          <t>11570</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19982</t>
+          <t>20739</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>36,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>63,59%</t>
+          <t>66,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>25591</t>
+          <t>26141</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>38011</t>
+          <t>37912</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>43,21%</t>
+          <t>44,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>64,18%</t>
+          <t>64,01%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>7751</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15431</t>
+          <t>15977</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>55,49%</t>
+          <t>57,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>11440</t>
+          <t>10683</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>19996</t>
+          <t>19852</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>63,64%</t>
+          <t>63,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>21217</t>
+          <t>21316</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>33637</t>
+          <t>33087</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>35,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>56,79%</t>
+          <t>55,86%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7516</t>
+          <t>7333</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14138</t>
+          <t>14435</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>39,06%</t>
+          <t>38,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>73,47%</t>
+          <t>75,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13843</t>
+          <t>13175</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20676</t>
+          <t>20638</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>56,12%</t>
+          <t>53,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>83,83%</t>
+          <t>83,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22949</t>
+          <t>22579</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>32876</t>
+          <t>32891</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>52,27%</t>
+          <t>51,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>74,87%</t>
+          <t>74,91%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5105</t>
+          <t>4808</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11727</t>
+          <t>11910</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>60,94%</t>
+          <t>61,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3989</t>
+          <t>4027</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10822</t>
+          <t>11490</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>43,88%</t>
+          <t>46,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>11032</t>
+          <t>11017</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>20959</t>
+          <t>21329</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>47,73%</t>
+          <t>48,58%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8789</t>
+          <t>9608</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16651</t>
+          <t>16583</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>41,6%</t>
+          <t>45,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>78,81%</t>
+          <t>78,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12608</t>
+          <t>13169</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20974</t>
+          <t>20941</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>48,4%</t>
+          <t>50,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>80,52%</t>
+          <t>80,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>24434</t>
+          <t>25088</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>35475</t>
+          <t>35622</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>51,79%</t>
+          <t>53,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>75,51%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4477</t>
+          <t>4545</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12339</t>
+          <t>11520</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>58,4%</t>
+          <t>54,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5074</t>
+          <t>5107</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>13440</t>
+          <t>12879</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>51,6%</t>
+          <t>49,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>11701</t>
+          <t>11554</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>22742</t>
+          <t>22088</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>48,21%</t>
+          <t>46,82%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>43961</t>
+          <t>44459</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>58425</t>
+          <t>58200</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>53,45%</t>
+          <t>54,06%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>71,04%</t>
+          <t>70,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>53943</t>
+          <t>54405</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>70547</t>
+          <t>69358</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>54,88%</t>
+          <t>55,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>71,78%</t>
+          <t>70,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>102383</t>
+          <t>102009</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>123457</t>
+          <t>122446</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>56,71%</t>
+          <t>56,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>68,39%</t>
+          <t>67,83%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>23817</t>
+          <t>24042</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>38281</t>
+          <t>37783</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>46,55%</t>
+          <t>45,94%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>27737</t>
+          <t>28926</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>44341</t>
+          <t>43879</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>29,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>45,12%</t>
+          <t>44,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>57070</t>
+          <t>58081</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>78144</t>
+          <t>78518</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>32,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>43,29%</t>
+          <t>43,49%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si dicha enfermedad o dolencia continuada le ha afectado para realizar actividades de ocio en 2016 (tasa de respuesta: 99,32%)</t>
+          <t>Menores según si dicha enfermedad o dolencia continuada le ha afectado para realizar actividades de ocio como pasear, ir al cine, hacer deporte, etc en 2016 (tasa de respuesta: 99,32%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>826</t>
+          <t>778</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5912</t>
+          <t>5796</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>72,37%</t>
+          <t>70,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2969</t>
+          <t>3165</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8011</t>
+          <t>8001</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>82,51%</t>
+          <t>82,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5304</t>
+          <t>5477</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12396</t>
+          <t>12805</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>69,33%</t>
+          <t>71,62%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2257</t>
+          <t>2373</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7343</t>
+          <t>7391</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>90,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1698</t>
+          <t>1708</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6740</t>
+          <t>6544</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>69,42%</t>
+          <t>67,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5482</t>
+          <t>5073</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12574</t>
+          <t>12401</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>70,33%</t>
+          <t>69,36%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4693</t>
+          <t>4616</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11686</t>
+          <t>11747</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>59,64%</t>
+          <t>59,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>7280</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14305</t>
+          <t>14719</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>71,38%</t>
+          <t>73,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14071</t>
+          <t>13708</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>24033</t>
+          <t>23554</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>34,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>60,63%</t>
+          <t>59,43%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7910</t>
+          <t>7849</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14903</t>
+          <t>14980</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>40,36%</t>
+          <t>40,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>76,05%</t>
+          <t>76,44%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>5736</t>
+          <t>5322</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>12935</t>
+          <t>12761</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>64,54%</t>
+          <t>63,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>15603</t>
+          <t>16082</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>25565</t>
+          <t>25928</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>39,37%</t>
+          <t>40,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>64,5%</t>
+          <t>65,42%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2938</t>
+          <t>2871</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7621</t>
+          <t>7599</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>84,6%</t>
+          <t>84,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3967</t>
+          <t>3959</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8418</t>
+          <t>8371</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>43,74%</t>
+          <t>43,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>92,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8287</t>
+          <t>8472</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14858</t>
+          <t>14679</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>45,84%</t>
+          <t>46,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>82,19%</t>
+          <t>81,2%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1387</t>
+          <t>1409</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6070</t>
+          <t>6137</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>67,39%</t>
+          <t>68,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>697</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5101</t>
+          <t>5109</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>56,26%</t>
+          <t>56,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3219</t>
+          <t>3398</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>9790</t>
+          <t>9605</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>54,16%</t>
+          <t>53,14%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4551</t>
+          <t>4587</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9628</t>
+          <t>9587</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>43,97%</t>
+          <t>44,32%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2742</t>
+          <t>2707</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8475</t>
+          <t>8468</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>67,11%</t>
+          <t>67,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8981</t>
+          <t>8908</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16954</t>
+          <t>16668</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>39,08%</t>
+          <t>38,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>73,78%</t>
+          <t>72,54%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>722</t>
+          <t>763</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5799</t>
+          <t>5763</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>56,03%</t>
+          <t>55,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4154</t>
+          <t>4161</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>9887</t>
+          <t>9922</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>32,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,28%</t>
+          <t>78,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6024</t>
+          <t>6310</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>13997</t>
+          <t>14070</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>60,92%</t>
+          <t>61,23%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18596</t>
+          <t>18533</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>30253</t>
+          <t>29516</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>39,46%</t>
+          <t>39,33%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>64,2%</t>
+          <t>62,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>21865</t>
+          <t>22748</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>33701</t>
+          <t>34242</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>42,5%</t>
+          <t>44,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>65,51%</t>
+          <t>66,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>44075</t>
+          <t>45337</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>60958</t>
+          <t>61043</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>44,71%</t>
+          <t>46,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>61,84%</t>
+          <t>61,93%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16870</t>
+          <t>17607</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>28527</t>
+          <t>28590</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>60,54%</t>
+          <t>60,67%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17746</t>
+          <t>17205</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>29582</t>
+          <t>28699</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>33,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>57,5%</t>
+          <t>55,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>37612</t>
+          <t>37527</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>54495</t>
+          <t>53233</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>38,16%</t>
+          <t>38,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>55,29%</t>
+          <t>54,0%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si dicha enfermedad o dolencia continuada le ha afectado para realizar actividades de ocio en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores según si dicha enfermedad o dolencia continuada le ha afectado para realizar actividades de ocio como pasear, ir al cine, hacer deporte, etc en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,7 +6574,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9300</t>
+          <t>8963</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -6589,7 +6589,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>77,46%</t>
+          <t>74,65%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -6609,7 +6609,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18891</t>
+          <t>18424</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -6624,7 +6624,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>78,94%</t>
+          <t>76,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>30275</t>
+          <t>29755</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>35470</t>
+          <t>35489</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>82,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,75%</t>
         </is>
       </c>
     </row>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2706</t>
+          <t>3043</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6707,7 +6707,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6727,7 +6727,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5040</t>
+          <t>5507</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6742,7 +6742,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>467</t>
+          <t>448</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5662</t>
+          <t>6182</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>17,2%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16029</t>
+          <t>16301</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21043</t>
+          <t>21064</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>75,04%</t>
+          <t>76,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12064</t>
+          <t>12054</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20449</t>
+          <t>20007</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>46,51%</t>
+          <t>46,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>78,85%</t>
+          <t>77,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>30569</t>
+          <t>30145</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>40854</t>
+          <t>41347</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>64,63%</t>
+          <t>63,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>87,42%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>317</t>
+          <t>296</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5331</t>
+          <t>5059</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>5486</t>
+          <t>5928</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13871</t>
+          <t>13881</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>53,49%</t>
+          <t>53,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6441</t>
+          <t>5948</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>16726</t>
+          <t>17150</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>35,37%</t>
+          <t>36,26%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8802</t>
+          <t>8594</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13808</t>
+          <t>13767</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>60,66%</t>
+          <t>59,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10353</t>
+          <t>10513</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17990</t>
+          <t>17888</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>49,4%</t>
+          <t>50,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>85,83%</t>
+          <t>85,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21558</t>
+          <t>21336</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30534</t>
+          <t>30514</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>60,78%</t>
+          <t>60,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>86,09%</t>
+          <t>86,03%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>702</t>
+          <t>743</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5708</t>
+          <t>5916</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>40,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2970</t>
+          <t>3072</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10607</t>
+          <t>10447</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>50,6%</t>
+          <t>49,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4935</t>
+          <t>4955</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>13911</t>
+          <t>14133</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>39,22%</t>
+          <t>39,85%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5527</t>
+          <t>5049</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11683</t>
+          <t>11573</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>32,22%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>74,54%</t>
+          <t>73,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15483</t>
+          <t>15767</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23818</t>
+          <t>23640</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>54,9%</t>
+          <t>55,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>83,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>23154</t>
+          <t>22811</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>33985</t>
+          <t>34378</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>52,77%</t>
+          <t>51,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>77,46%</t>
+          <t>78,35%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3990</t>
+          <t>4100</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10146</t>
+          <t>10624</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>64,73%</t>
+          <t>67,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4386</t>
+          <t>4564</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>12721</t>
+          <t>12437</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>45,1%</t>
+          <t>44,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>9892</t>
+          <t>9499</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>20723</t>
+          <t>21066</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>47,23%</t>
+          <t>48,01%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>45028</t>
+          <t>45687</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>56624</t>
+          <t>56596</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>70,86%</t>
+          <t>71,89%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>89,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>64030</t>
+          <t>63923</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>82179</t>
+          <t>82207</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>64,66%</t>
+          <t>64,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>82,99%</t>
+          <t>83,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>113774</t>
+          <t>114571</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>134739</t>
+          <t>135763</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>69,98%</t>
+          <t>70,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>82,88%</t>
+          <t>83,51%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6924</t>
+          <t>6952</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18520</t>
+          <t>17861</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>16850</t>
+          <t>16822</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>34999</t>
+          <t>35106</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>35,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>27839</t>
+          <t>26815</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>48804</t>
+          <t>48007</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>29,53%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP09B02-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP09B02-Habitat-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>14825</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>11825</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>16263</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>87,91%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>70,12%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>96,44%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>7016</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>4281</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>9120</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>4193</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>8870</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>71,85%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>43,84%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>93,39%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>14825</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>11808</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>16266</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>87,91%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>70,02%</t>
+          <t>42,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>90,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17402</t>
+          <t>17692</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24260</t>
+          <t>24611</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>65,35%</t>
+          <t>66,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>92,42%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2039</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>601</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>5039</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>12,09%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>3,56%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>29,88%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>2749</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>645</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>5484</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>895</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>5572</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>28,15%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>6,61%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>56,16%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>2039</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>5056</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>12,09%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>57,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2370</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>9228</t>
+          <t>8938</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>33,56%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>16864</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>16864</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>16864</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>9765</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>9765</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>9765</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>16864</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>16864</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>16864</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>20895</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>16755</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>23686</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>75,47%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>60,52%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>85,55%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>11834</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>8724</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>13759</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>8746</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>13749</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>78,76%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>58,06%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>91,57%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>20895</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>16589</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>24208</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>75,47%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>59,92%</t>
+          <t>58,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>87,44%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>27523</t>
+          <t>27264</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>36194</t>
+          <t>36141</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>64,44%</t>
+          <t>63,83%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>84,74%</t>
+          <t>84,62%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>6791</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>10931</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>24,53%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>14,45%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>39,48%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>3192</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1267</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>6302</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>1277</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>6280</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>21,24%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>8,43%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>41,94%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>6791</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>3478</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>11097</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>24,53%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>40,08%</t>
+          <t>41,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6518</t>
+          <t>6571</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>15189</t>
+          <t>15448</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>36,17%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>27686</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>27686</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>27686</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>15026</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>15026</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>15026</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>27686</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>27686</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>27686</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>12619</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>9326</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>14698</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>82,12%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>60,69%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>95,65%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>4935</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2533</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>6729</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>2451</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>6794</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>62,72%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>32,19%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>85,51%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>12619</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>9831</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>14640</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>82,12%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>63,98%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>86,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13839</t>
+          <t>13776</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20305</t>
+          <t>20187</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>59,56%</t>
+          <t>59,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>87,38%</t>
+          <t>86,88%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2747</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>668</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>6040</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>17,88%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>4,35%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>39,31%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>2934</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>1140</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>5336</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>1075</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>5418</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>37,28%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>14,49%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>67,81%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>2747</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>726</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>5535</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>17,88%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
+          <t>68,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2931</t>
+          <t>3049</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>9397</t>
+          <t>9460</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>40,44%</t>
+          <t>40,71%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>15366</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>15366</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>15366</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>7869</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>7869</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>7869</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>15366</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>15366</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>15366</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>18992</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>15566</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>20981</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>85,49%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>70,07%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>94,44%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>15610</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>11118</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>19111</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>11100</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>18979</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>68,13%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>48,52%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>83,41%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>18992</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>15656</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>20968</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>85,49%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>70,47%</t>
+          <t>48,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>82,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>29107</t>
+          <t>29258</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>38986</t>
+          <t>38871</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>64,5%</t>
+          <t>64,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>86,39%</t>
+          <t>86,14%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>3223</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>6649</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>14,51%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>5,56%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>29,93%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>7303</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>3802</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>11795</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>3934</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>11813</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>31,87%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>16,59%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>51,48%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>3223</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>1247</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>6559</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>14,51%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>51,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6141</t>
+          <t>6256</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>16020</t>
+          <t>15869</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>35,16%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>22215</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>22215</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>22215</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>22913</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>22913</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>22913</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>22215</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>22215</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>22215</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>67331</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>61277</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>72241</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>81,98%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>74,61%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>87,96%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>59</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>39396</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>33479</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>44264</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>32809</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>44199</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>70,89%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>60,24%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>79,65%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>67331</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>61042</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>72400</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>81,98%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>74,32%</t>
+          <t>59,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>79,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>98413</t>
+          <t>98818</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>114016</t>
+          <t>114513</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>71,47%</t>
+          <t>71,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>82,8%</t>
+          <t>83,16%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>14800</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>9890</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>20854</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>18,02%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>12,04%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>25,39%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>16178</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>11310</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>22095</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>11375</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>22765</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>29,11%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>20,35%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>39,76%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>14800</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>9731</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>21089</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>18,02%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>40,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>23689</t>
+          <t>23192</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>39292</t>
+          <t>38887</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>28,24%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>82131</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>82131</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>82131</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>82</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>55574</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>55574</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>55574</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>82131</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>82131</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>82131</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2675,67 +2675,67 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>10994</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>7369</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>13904</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>68,08%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>45,63%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>86,1%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>11213</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>7715</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>12774</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>7992</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>13361</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>79,72%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>54,85%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>90,82%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>10994</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>7486</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>13896</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>68,08%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>56,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>86,05%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17352</t>
+          <t>16958</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25926</t>
+          <t>25429</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>57,43%</t>
+          <t>56,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>85,81%</t>
+          <t>84,16%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>5155</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2245</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>8780</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>31,92%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>13,9%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>54,37%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>2852</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>1291</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>6350</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>704</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>6073</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>20,28%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>9,18%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>45,15%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>5155</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>2253</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>8663</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>31,92%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>53,65%</t>
+          <t>43,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4288</t>
+          <t>4785</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12862</t>
+          <t>13256</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,57%</t>
+          <t>43,87%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>16149</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>16149</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>16149</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>14065</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>14065</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>14065</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>16149</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>16149</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>16149</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>16167</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>11596</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>21221</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>51,45%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>36,91%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>67,54%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>16091</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>11829</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>20055</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>11529</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>20001</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>57,87%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>42,54%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>72,12%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>16167</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>11570</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>20739</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>51,45%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>36,82%</t>
+          <t>41,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>66,0%</t>
+          <t>71,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26141</t>
+          <t>25746</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>37912</t>
+          <t>38084</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>44,14%</t>
+          <t>43,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>64,01%</t>
+          <t>64,3%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>15255</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>10201</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>19826</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>48,55%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>32,46%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>63,09%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>11715</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>7751</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>15977</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>7805</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>16277</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>42,13%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>27,88%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>57,46%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>15255</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>10683</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>19852</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>48,55%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>63,18%</t>
+          <t>58,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>21316</t>
+          <t>21144</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>33087</t>
+          <t>33482</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>35,99%</t>
+          <t>35,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>55,86%</t>
+          <t>56,53%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>31422</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>31422</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>31422</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>27806</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>27806</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>27806</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>31422</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>31422</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>31422</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>17426</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>13229</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>20919</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>70,65%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>53,63%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>84,81%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>10873</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>7333</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>14435</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>7672</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>14297</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>56,5%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>38,11%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>75,01%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>17426</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>13175</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>20638</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>70,65%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>53,42%</t>
+          <t>39,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>83,67%</t>
+          <t>74,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22579</t>
+          <t>23053</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>32891</t>
+          <t>33053</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>51,42%</t>
+          <t>52,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>74,91%</t>
+          <t>75,28%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>7239</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>3746</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>11436</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>29,35%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>15,19%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>46,37%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>8370</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>4808</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>11910</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>4946</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>11571</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>43,5%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>24,99%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>61,89%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>7239</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>4027</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>11490</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>29,35%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>46,58%</t>
+          <t>60,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>11017</t>
+          <t>10855</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>21329</t>
+          <t>20855</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>48,58%</t>
+          <t>47,5%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>24665</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>24665</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>24665</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>19243</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>19243</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>19243</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>24665</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>24665</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>24665</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>17420</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>13096</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>20869</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>66,88%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>50,28%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>80,12%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>13097</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>9608</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>16583</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>8800</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>16802</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>61,99%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>45,48%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>78,49%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>17420</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>13169</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>20941</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>66,88%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>50,56%</t>
+          <t>41,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>80,4%</t>
+          <t>79,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>25088</t>
+          <t>25204</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>35622</t>
+          <t>36169</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>53,18%</t>
+          <t>53,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>75,51%</t>
+          <t>76,67%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>8628</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>5179</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>12952</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>33,12%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>19,88%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>49,72%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>8031</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>4545</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>11520</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>4326</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>12328</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>38,01%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>21,51%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>54,52%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>8628</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>5107</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>12879</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>33,12%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>49,44%</t>
+          <t>58,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>11554</t>
+          <t>11007</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>22088</t>
+          <t>21972</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>46,82%</t>
+          <t>46,57%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>26048</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>26048</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>26048</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>21128</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>21128</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>21128</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>26048</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>26048</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>26048</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>62007</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>54369</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>69759</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>63,09%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>55,32%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>70,98%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>74</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>51274</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>44459</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>58200</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>43562</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>57908</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>62,34%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>54,06%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>70,77%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>62007</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>54405</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>69358</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>63,09%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>55,36%</t>
+          <t>52,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>70,57%</t>
+          <t>70,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>102009</t>
+          <t>101791</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>122446</t>
+          <t>122853</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>56,51%</t>
+          <t>56,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>67,83%</t>
+          <t>68,05%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>36277</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>28525</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>43915</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>36,91%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>29,02%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>44,68%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>30968</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>24042</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>37783</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>24334</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>38680</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>37,66%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>29,23%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>45,94%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>36277</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>28926</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>43879</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>36,91%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>44,64%</t>
+          <t>47,03%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>58081</t>
+          <t>57674</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>78518</t>
+          <t>78736</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>43,49%</t>
+          <t>43,61%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>98284</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>98284</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>98284</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>121</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>82242</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>82242</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>82242</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>98284</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>98284</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>98284</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,72 +4617,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5815</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2993</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>7951</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>59,89%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>30,82%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>81,89%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>3205</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>778</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5796</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>6158</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>39,23%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>9,52%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>70,96%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>5815</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>3165</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>8001</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>59,89%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>82,4%</t>
+          <t>75,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5477</t>
+          <t>5642</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12805</t>
+          <t>12544</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>31,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>71,62%</t>
+          <t>70,16%</t>
         </is>
       </c>
     </row>
@@ -4730,72 +4730,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>3894</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1758</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>6716</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>40,11%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>18,11%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>69,18%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>4964</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>2373</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>7391</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>7224</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>60,77%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>29,04%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>90,48%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>3894</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>1708</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>6544</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>40,11%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>67,4%</t>
+          <t>88,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5073</t>
+          <t>5334</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12401</t>
+          <t>12236</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>69,36%</t>
+          <t>68,44%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>9709</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>9709</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>9709</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>8169</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>8169</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>8169</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>9709</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>9709</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>9709</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>10627</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>6538</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>14175</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>53,03%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>32,62%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>70,73%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>8191</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>4616</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>11747</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>4881</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>11871</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>41,8%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>23,56%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>59,95%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>10627</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>7280</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>14719</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>53,03%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>73,44%</t>
+          <t>60,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13708</t>
+          <t>13354</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23554</t>
+          <t>23948</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>33,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>59,43%</t>
+          <t>60,42%</t>
         </is>
       </c>
     </row>
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>9414</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>5866</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>13503</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>46,97%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>29,27%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>67,38%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>11405</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>7849</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>14980</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>7725</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>14715</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>58,2%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>40,05%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>76,44%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>9414</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>5322</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>12761</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>46,97%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>39,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>63,67%</t>
+          <t>75,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>16082</t>
+          <t>15688</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>25928</t>
+          <t>26282</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>40,57%</t>
+          <t>39,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>65,42%</t>
+          <t>66,31%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>20041</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>20041</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>20041</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>19596</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>19596</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>19596</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>20041</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>20041</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>20041</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>6402</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3789</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>8385</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>70,6%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>41,78%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>92,47%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>5319</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2871</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>7599</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>2967</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>7373</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>59,05%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>31,87%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>84,36%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>6402</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>3959</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>8371</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>70,6%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>43,66%</t>
+          <t>32,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>81,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8472</t>
+          <t>8318</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14679</t>
+          <t>14456</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>46,86%</t>
+          <t>46,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>81,2%</t>
+          <t>79,97%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2666</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>683</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>5279</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>29,4%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>7,53%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>58,22%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>3689</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>1409</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>6137</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>1635</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>6041</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>40,95%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>15,64%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>68,13%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>2666</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>697</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>5109</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>29,4%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>56,34%</t>
+          <t>67,06%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3398</t>
+          <t>3621</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>9605</t>
+          <t>9759</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>53,14%</t>
+          <t>53,99%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>9068</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>9068</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>9068</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>9008</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>9008</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>9008</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>9068</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>9068</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>9068</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>5584</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2810</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>8943</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>44,22%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>22,25%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>70,81%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>7477</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>4587</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>9587</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>4378</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>9522</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>72,24%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>44,32%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>92,63%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>5584</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>2707</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>8468</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>44,22%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>42,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>67,05%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8908</t>
+          <t>8730</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16668</t>
+          <t>16912</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>38,77%</t>
+          <t>37,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>72,54%</t>
+          <t>73,6%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>7045</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>3686</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>9819</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>55,78%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>29,19%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>77,75%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>2873</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>763</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>5763</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>828</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>5972</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>27,76%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>7,37%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>55,68%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>7045</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>4161</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>9922</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>55,78%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,56%</t>
+          <t>57,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6310</t>
+          <t>6066</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>14070</t>
+          <t>14248</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>61,23%</t>
+          <t>62,01%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>12629</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>12629</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>12629</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>10350</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>10350</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>10350</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>12629</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>12629</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>12629</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>28429</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>22300</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>34394</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>55,26%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>43,35%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>66,85%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>24192</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>18533</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>29516</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>18689</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>29474</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>51,34%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>39,33%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>62,64%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>28429</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>22748</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>34242</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>55,26%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>44,22%</t>
+          <t>39,66%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>66,56%</t>
+          <t>62,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>45337</t>
+          <t>44687</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>61043</t>
+          <t>60342</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>46,0%</t>
+          <t>45,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>61,93%</t>
+          <t>61,22%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>23018</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>17053</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>29147</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>44,74%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>33,15%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>56,65%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>22931</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>17607</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>28590</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>17649</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>28434</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>48,66%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>37,36%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>60,67%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>23018</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>17205</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>28699</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>44,74%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>37,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>55,78%</t>
+          <t>60,34%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>37527</t>
+          <t>38228</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>53233</t>
+          <t>53883</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>38,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>54,0%</t>
+          <t>54,66%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>51447</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>51447</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>51447</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>47123</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>47123</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>47123</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>51447</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>51447</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>51447</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6569,27 +6569,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>11171</t>
+          <t>19060</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8963</t>
+          <t>15772</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12006</t>
+          <t>20633</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>74,65%</t>
+          <t>76,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -6604,27 +6604,27 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>22175</t>
+          <t>11695</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18424</t>
+          <t>9657</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23931</t>
+          <t>12511</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>76,99%</t>
+          <t>77,19%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -6639,17 +6639,17 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>33346</t>
+          <t>30755</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>29755</t>
+          <t>27577</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>35489</t>
+          <t>32562</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>82,8%</t>
+          <t>83,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,25%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1573</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>4861</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>7,62%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>23,56%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>835</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>816</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>3043</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>6,96%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>2854</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>6,52%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>25,35%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>1756</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>5507</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>7,34%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,17 +6752,17 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>2591</t>
+          <t>2389</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>448</t>
+          <t>582</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6182</t>
+          <t>5567</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>16,8%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>20633</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>20633</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>20633</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>12006</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>12006</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>12006</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>23931</t>
+          <t>12511</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>23931</t>
+          <t>12511</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>23931</t>
+          <t>12511</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>35937</t>
+          <t>33144</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>35937</t>
+          <t>33144</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>35937</t>
+          <t>33144</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>14648</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>10194</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>18302</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>62,85%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>43,74%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>78,53%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>19596</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>16301</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>21064</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>91,74%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>76,32%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>98,62%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>16396</t>
+          <t>14397</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12054</t>
+          <t>11555</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20007</t>
+          <t>15802</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>63,22%</t>
+          <t>89,17%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>46,48%</t>
+          <t>71,56%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>77,14%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>35992</t>
+          <t>29046</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>30145</t>
+          <t>24388</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>41347</t>
+          <t>32974</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>76,1%</t>
+          <t>73,62%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>63,74%</t>
+          <t>61,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>87,42%</t>
+          <t>83,57%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>8659</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>5005</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>13113</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>37,15%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>21,47%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>56,26%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>1764</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>296</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>5059</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>8,26%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1,38%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>23,68%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>9539</t>
+          <t>1749</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>5928</t>
+          <t>344</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13881</t>
+          <t>4591</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>36,78%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>53,52%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>11303</t>
+          <t>10408</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5948</t>
+          <t>6480</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>17150</t>
+          <t>15066</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>38,19%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>23307</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>23307</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>23307</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>21360</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>21360</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>21360</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>25935</t>
+          <t>16146</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>25935</t>
+          <t>16146</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>25935</t>
+          <t>16146</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>47295</t>
+          <t>39454</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>47295</t>
+          <t>39454</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>47295</t>
+          <t>39454</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>13955</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>9619</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>17224</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>70,27%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>48,44%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>86,74%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>12130</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>8594</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>13767</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>83,59%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>59,23%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>94,88%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>14664</t>
+          <t>12332</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10513</t>
+          <t>8626</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17888</t>
+          <t>14052</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>69,96%</t>
+          <t>83,56%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>50,16%</t>
+          <t>58,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>85,34%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>26793</t>
+          <t>26286</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21336</t>
+          <t>20990</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30514</t>
+          <t>30001</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>75,54%</t>
+          <t>75,94%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>60,15%</t>
+          <t>60,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>86,67%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>5903</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2634</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>10239</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>29,73%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>13,26%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>51,56%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>2380</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>743</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>5916</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>16,41%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>5,12%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>40,77%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6296</t>
+          <t>2427</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3072</t>
+          <t>707</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10447</t>
+          <t>6133</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>49,84%</t>
+          <t>41,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>8676</t>
+          <t>8330</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4955</t>
+          <t>4615</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>14133</t>
+          <t>13626</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>39,85%</t>
+          <t>39,36%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>19858</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>19858</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>19858</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>14510</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>14510</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>14510</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>20960</t>
+          <t>14759</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>20960</t>
+          <t>14759</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>20960</t>
+          <t>14759</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>35469</t>
+          <t>34616</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>35469</t>
+          <t>34616</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>35469</t>
+          <t>34616</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>18020</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>13760</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>21017</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>71,87%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>54,88%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>83,82%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>8645</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>5049</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>11573</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>55,16%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>32,22%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>73,84%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>20213</t>
+          <t>8418</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15767</t>
+          <t>5232</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23640</t>
+          <t>11915</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>71,67%</t>
+          <t>53,73%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>55,9%</t>
+          <t>33,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>83,82%</t>
+          <t>76,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>28858</t>
+          <t>26438</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>22811</t>
+          <t>21208</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>34378</t>
+          <t>31067</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>65,77%</t>
+          <t>64,9%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>51,99%</t>
+          <t>52,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>78,35%</t>
+          <t>76,26%</t>
         </is>
       </c>
     </row>
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>7053</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>4056</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>11313</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>28,13%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>16,18%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>45,12%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>7028</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>4100</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>10624</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>44,84%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>26,16%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>67,78%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>7991</t>
+          <t>7248</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4564</t>
+          <t>3751</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>12437</t>
+          <t>10434</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>46,27%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>66,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>15019</t>
+          <t>14301</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>9499</t>
+          <t>9672</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>21066</t>
+          <t>19531</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>35,1%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>48,01%</t>
+          <t>47,94%</t>
         </is>
       </c>
     </row>
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>25073</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>25073</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>25073</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>15673</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>15673</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>15673</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>28204</t>
+          <t>15666</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>28204</t>
+          <t>15666</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>28204</t>
+          <t>15666</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>43877</t>
+          <t>40739</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>43877</t>
+          <t>40739</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>43877</t>
+          <t>40739</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>65683</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>58089</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>73728</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>73,91%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>65,36%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>82,96%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>51540</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>45687</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>56596</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>81,1%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>71,89%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>89,06%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>73448</t>
+          <t>46842</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>63923</t>
+          <t>40889</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>82207</t>
+          <t>51248</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>74,17%</t>
+          <t>79,28%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>64,55%</t>
+          <t>69,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>83,01%</t>
+          <t>86,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>124989</t>
+          <t>112525</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>114571</t>
+          <t>102983</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>135763</t>
+          <t>121641</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>76,88%</t>
+          <t>76,05%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>70,47%</t>
+          <t>69,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>83,51%</t>
+          <t>82,22%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>23188</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>15143</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>30782</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>26,09%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>17,04%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>34,64%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>12008</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>6952</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>17861</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>18,9%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>10,94%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>28,11%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>25581</t>
+          <t>12240</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>16822</t>
+          <t>7834</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>35106</t>
+          <t>18193</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>37589</t>
+          <t>35428</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>26815</t>
+          <t>26312</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>48007</t>
+          <t>44970</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>30,39%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>88871</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>88871</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>88871</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>63548</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>63548</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>63548</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>99029</t>
+          <t>59082</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>99029</t>
+          <t>59082</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>99029</t>
+          <t>59082</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>162578</t>
+          <t>147953</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>162578</t>
+          <t>147953</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>162578</t>
+          <t>147953</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
